--- a/corpus/xlsx/level-076/template.xlsx
+++ b/corpus/xlsx/level-076/template.xlsx
@@ -19,19 +19,19 @@
     <sheet name="Region 10 山田" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="ItemRange1">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange2">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange3">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange4">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange5">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange6">'Report'!$A$40:$D$40</definedName>
+    <definedName name="ItemRange1">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange2">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange3">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange4">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange5">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange6">'Report'!$A$40:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <si>
     <r>
       <rPr>
@@ -129,7 +129,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -170,14 +178,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -203,7 +203,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -219,15 +227,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">u</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
     </r>
     <r>
       <rPr>
@@ -259,15 +267,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -285,7 +285,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -326,14 +334,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -359,7 +359,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -408,14 +416,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -441,7 +441,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -497,15 +505,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -523,7 +523,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -579,15 +587,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
   <si>
@@ -781,39 +781,31 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">#e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ac</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">h i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">te</t>
+      <t xml:space="preserve">{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
     </r>
     <r>
       <rPr>
@@ -829,15 +821,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">}}{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{n</t>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
     </r>
     <r>
       <rPr>
@@ -853,7 +853,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">e}}</t>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -863,31 +863,55 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">u</t>
+      <t xml:space="preserve">{d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">te</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">qu</t>
     </r>
     <r>
       <rPr>
@@ -903,39 +927,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">y</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">ti</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ty}</t>
     </r>
   </si>
   <si>
@@ -953,6 +953,80 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">pr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ic</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
       <t xml:space="preserve">{</t>
     </r>
     <r>
@@ -961,55 +1035,71 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">p</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">1]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">am</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -1973,7 +2063,7 @@
     <xdr:ext cx="914400" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2004,7 +2094,7 @@
     <xdr:ext cx="960120" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2035,7 +2125,7 @@
     <xdr:ext cx="1005840" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2066,7 +2156,7 @@
     <xdr:ext cx="1051560" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2097,7 +2187,7 @@
     <xdr:ext cx="1097280" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2128,7 +2218,7 @@
     <xdr:ext cx="1143000" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2159,7 +2249,7 @@
     <xdr:ext cx="1188720" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2190,7 +2280,7 @@
     <xdr:ext cx="1234440" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2221,7 +2311,7 @@
     <xdr:ext cx="1280160" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2252,7 +2342,7 @@
     <xdr:ext cx="1325880" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2277,8 +2367,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D40" totalsRowShown="0">
-  <autoFilter ref="A39:D40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D41" totalsRowShown="0">
+  <autoFilter ref="A39:D41"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Quantity"/>
@@ -2291,7 +2381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2618,14 +2708,14 @@
         <f>B40*C40</f>
         <v>0</v>
       </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{/each}}</t>
-        </is>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A39:D40"/>
+  <autoFilter ref="A39:D41"/>
   <mergeCells count="10">
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
@@ -2638,25 +2728,25 @@
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A24:C24"/>
   </mergeCells>
-  <conditionalFormatting sqref="B40:B40">
+  <conditionalFormatting sqref="B40:B41">
     <cfRule type="cellIs" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B41">
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C41">
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D41">
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E41">
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
@@ -2675,7 +2765,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2699,7 +2789,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2723,7 +2813,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2747,7 +2837,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2771,7 +2861,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2795,7 +2885,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2819,7 +2909,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2843,7 +2933,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2867,7 +2957,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2891,7 +2981,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2915,7 +3005,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
